--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487405_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487405_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.766</v>
+        <v>7.1092</v>
       </c>
       <c r="E2" t="n">
-        <v>6.4366</v>
+        <v>5.0203</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3295</v>
+        <v>2.0889</v>
       </c>
       <c r="G2" t="n">
         <v>5.6233</v>
@@ -610,13 +610,13 @@
         <v>1.9585</v>
       </c>
       <c r="S2" t="n">
-        <v>3.9107</v>
+        <v>2.2539</v>
       </c>
       <c r="T2" t="n">
-        <v>2.5378</v>
+        <v>1.1216</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3729</v>
+        <v>1.1323</v>
       </c>
       <c r="V2" t="n">
         <v>0.2113</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I. SAMA PEREZ</t>
+          <t>P. FERNANDEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3864</v>
+        <v>5.0014</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1201</v>
+        <v>5.4427</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2664</v>
+        <v>-0.4413</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5073</v>
+        <v>1.0362</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.3314</v>
+        <v>-3.0202</v>
       </c>
       <c r="I3" t="n">
-        <v>3.8387</v>
+        <v>4.0563</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3646</v>
+        <v>3.9902</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.1804</v>
+        <v>-1.1214</v>
       </c>
       <c r="L3" t="n">
-        <v>3.545</v>
+        <v>5.1116</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8573</v>
+        <v>-2.9541</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.151</v>
+        <v>-1.8988</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2937</v>
+        <v>-1.0552</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.5875</v>
+        <v>2.546</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.9377</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3502</v>
+        <v>2.546</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6417</v>
+        <v>0.5996</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1317</v>
+        <v>0.2358</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7735</v>
+        <v>0.3638</v>
       </c>
       <c r="V3" t="n">
-        <v>1.8249</v>
+        <v>0.8196</v>
       </c>
       <c r="W3" t="n">
-        <v>1.8249</v>
+        <v>1.2166</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.397</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. FERNANDEZ GONZALEZ</t>
+          <t>I. SAMA PEREZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8408</v>
+        <v>4.732</v>
       </c>
       <c r="E4" t="n">
-        <v>3.977</v>
+        <v>2.5459</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.1363</v>
+        <v>2.1862</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0362</v>
+        <v>2.5073</v>
       </c>
       <c r="H4" t="n">
-        <v>-3.0202</v>
+        <v>-1.3314</v>
       </c>
       <c r="I4" t="n">
-        <v>4.0563</v>
+        <v>3.8387</v>
       </c>
       <c r="J4" t="n">
-        <v>3.9902</v>
+        <v>3.3646</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.1214</v>
+        <v>-0.1804</v>
       </c>
       <c r="L4" t="n">
-        <v>5.1116</v>
+        <v>3.545</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.9541</v>
+        <v>-0.8573</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.8988</v>
+        <v>-1.151</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.0552</v>
+        <v>0.2937</v>
       </c>
       <c r="P4" t="n">
-        <v>2.546</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q4" t="n">
+        <v>-2.9377</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2.3502</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.9873</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.2941</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.6933</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.8249</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.8249</v>
+      </c>
+      <c r="X4" t="n">
         <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.546</v>
-      </c>
-      <c r="S4" t="n">
-        <v>-1.561</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-1.2298</v>
-      </c>
-      <c r="U4" t="n">
-        <v>-0.3312</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.8196</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.2166</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-0.397</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4126</v>
+        <v>2.944</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5549</v>
+        <v>2.819</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1423</v>
+        <v>0.125</v>
       </c>
       <c r="G5" t="n">
         <v>3.0649</v>
@@ -844,13 +844,13 @@
         <v>1.3709</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3323</v>
+        <v>0.8637</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0306</v>
+        <v>0.2335</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3629</v>
+        <v>0.6302</v>
       </c>
       <c r="V5" t="n">
         <v>-0.397</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1223</v>
+        <v>-0.253</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4499</v>
+        <v>0.2617</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3276</v>
+        <v>-0.5147</v>
       </c>
       <c r="G6" t="n">
         <v>-2.1945</v>
@@ -922,13 +922,13 @@
         <v>0.1958</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5191</v>
+        <v>1.1438</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8893</v>
+        <v>0.7010999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6298</v>
+        <v>0.4427</v>
       </c>
       <c r="V6" t="n">
         <v>0.6018</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. SYTAR</t>
+          <t>A. HERMIDA PEREZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2415</v>
+        <v>-0.3752</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5596</v>
+        <v>0.8668</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3181</v>
+        <v>-1.242</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.5201</v>
+        <v>0.5595</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.034</v>
+        <v>-0.3804</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4861</v>
+        <v>0.9399</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.8493000000000001</v>
+        <v>1.6314</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.883</v>
+        <v>0.2977</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0337</v>
+        <v>1.3337</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.6708</v>
+        <v>-1.0718</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.151</v>
+        <v>-0.6781</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5198</v>
+        <v>-0.3938</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1958</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1543</v>
+        <v>0.9792</v>
       </c>
       <c r="S7" t="n">
-        <v>3.1456</v>
+        <v>-0.3841</v>
       </c>
       <c r="T7" t="n">
-        <v>1.4221</v>
+        <v>0.2147</v>
       </c>
       <c r="U7" t="n">
-        <v>1.7235</v>
+        <v>-0.5987</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0629</v>
+        <v>-0.5507</v>
       </c>
       <c r="W7" t="n">
-        <v>0.8260999999999999</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.889</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. HERMIDA PEREZ</t>
+          <t>A. SYTAR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2821</v>
+        <v>-1.3259</v>
       </c>
       <c r="E8" t="n">
-        <v>1.1738</v>
+        <v>-1.243</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4559</v>
+        <v>-0.0829</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5595</v>
+        <v>-2.5201</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3804</v>
+        <v>-2.034</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9399</v>
+        <v>-0.4861</v>
       </c>
       <c r="J8" t="n">
-        <v>1.6314</v>
+        <v>-0.8493000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2977</v>
+        <v>-0.883</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3337</v>
+        <v>0.0337</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0718</v>
+        <v>-1.6708</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6781</v>
+        <v>-1.151</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3938</v>
+        <v>-0.5198</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.1958</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9792</v>
+        <v>2.1543</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2909</v>
+        <v>2.0613</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5217000000000001</v>
+        <v>0.7387</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8126</v>
+        <v>1.3226</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5507</v>
+        <v>-1.0629</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5507</v>
+        <v>-1.889</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. RAMOS DA CONCEIÇAO</t>
+          <t>C. DARRIBA VAZQUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6658</v>
+        <v>-1.3391</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1851</v>
+        <v>-3.5125</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4808</v>
+        <v>2.1735</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.4342</v>
+        <v>-1.1714</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.6608000000000001</v>
+        <v>-0.3783</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.7734</v>
+        <v>-0.7931</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.2228</v>
+        <v>-0.9182</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6618000000000001</v>
+        <v>-0.5189</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5610000000000001</v>
+        <v>-0.3993</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2114</v>
+        <v>-0.2532</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001</v>
+        <v>0.1406</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.2125</v>
+        <v>-0.3938</v>
       </c>
       <c r="P9" t="n">
+        <v>-1.9585</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-2.9377</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.9792</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.7815</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.6659</v>
+      </c>
+      <c r="W9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.493</v>
-      </c>
-      <c r="T9" t="n">
-        <v>-0.2376</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0.7306</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0.2754</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0.2754</v>
-      </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.6659</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. DARRIBA VAZQUEZ</t>
+          <t>S. RAMOS DA CONCEIÇAO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2558</v>
+        <v>-1.3783</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.5094</v>
+        <v>-0.6569</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2537</v>
+        <v>-0.7213000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.1714</v>
+        <v>-2.4342</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3783</v>
+        <v>-0.6608000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7931</v>
+        <v>-1.7734</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.9182</v>
+        <v>-1.2228</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5189</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.3993</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2532</v>
+        <v>-1.2114</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1406</v>
+        <v>0.001</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3938</v>
+        <v>-1.2125</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.9377</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9792</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2083</v>
+        <v>0.7806</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6534</v>
+        <v>0.2905</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8617</v>
+        <v>0.4901</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6659</v>
+        <v>0.2754</v>
       </c>
       <c r="W10" t="n">
+        <v>0.2754</v>
+      </c>
+      <c r="X10" t="n">
         <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0.6659</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.3395</v>
+        <v>-3.1837</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6231</v>
+        <v>-2.5207</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7164</v>
+        <v>-0.6629</v>
       </c>
       <c r="G11" t="n">
         <v>-1.2208</v>
@@ -1312,13 +1312,13 @@
         <v>0.1958</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3561</v>
+        <v>-0.2003</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0176</v>
+        <v>0.12</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3737</v>
+        <v>-0.3202</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>10.7434</v>
+        <v>11.9314</v>
       </c>
       <c r="E12" t="n">
-        <v>7.835099999999998</v>
+        <v>9.023300000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>2.9084</v>
+        <v>2.9085</v>
       </c>
       <c r="G12" t="n">
-        <v>3.250200000000002</v>
+        <v>3.2502</v>
       </c>
       <c r="H12" t="n">
         <v>-6.801600000000001</v>
@@ -1375,7 +1375,7 @@
         <v>-13.0621</v>
       </c>
       <c r="N12" t="n">
-        <v>-9.150600000000001</v>
+        <v>-9.150599999999999</v>
       </c>
       <c r="O12" t="n">
         <v>-3.9117</v>
@@ -1390,13 +1390,13 @@
         <v>12.7299</v>
       </c>
       <c r="S12" t="n">
-        <v>8.0427</v>
+        <v>9.230799999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>3.1054</v>
+        <v>4.2935</v>
       </c>
       <c r="U12" t="n">
-        <v>4.937399999999999</v>
+        <v>4.9376</v>
       </c>
       <c r="V12" t="n">
         <v>2.3883</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.2029</v>
+        <v>2.6464</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9529</v>
+        <v>3.2599</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.75</v>
+        <v>-0.6135</v>
       </c>
       <c r="G13" t="n">
         <v>7.5687</v>
@@ -1468,13 +1468,13 @@
         <v>3.1336</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.0179</v>
+        <v>-1.5744</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.3968</v>
+        <v>-1.0898</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6211</v>
+        <v>-0.4846</v>
       </c>
       <c r="V13" t="n">
         <v>-1.3894</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.9507</v>
+        <v>1.6511</v>
       </c>
       <c r="E14" t="n">
-        <v>3.4674</v>
+        <v>3.0581</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.5167</v>
+        <v>-1.407</v>
       </c>
       <c r="G14" t="n">
         <v>1.6056</v>
@@ -1546,13 +1546,13 @@
         <v>2.3502</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0419</v>
+        <v>-0.3416</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0576</v>
+        <v>-0.3517</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.09959999999999999</v>
+        <v>0.0102</v>
       </c>
       <c r="V14" t="n">
         <v>-1.7673</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.3206</v>
+        <v>-0.5179</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.6224</v>
+        <v>-0.9294</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3017</v>
+        <v>0.4115</v>
       </c>
       <c r="G15" t="n">
         <v>-0.2811</v>
@@ -1624,13 +1624,13 @@
         <v>2.546</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7065</v>
+        <v>-0.9038</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1206</v>
+        <v>-0.4276</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.586</v>
+        <v>-0.4762</v>
       </c>
       <c r="V15" t="n">
         <v>0.2754</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.9579</v>
+        <v>-2.6182</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0324</v>
+        <v>-1.1581</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.9255</v>
+        <v>-1.4601</v>
       </c>
       <c r="G16" t="n">
         <v>-2.2487</v>
@@ -1702,13 +1702,13 @@
         <v>1.1751</v>
       </c>
       <c r="S16" t="n">
-        <v>1.7032</v>
+        <v>0.0429</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9181</v>
+        <v>-0.2076</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7852</v>
+        <v>0.2506</v>
       </c>
       <c r="V16" t="n">
         <v>-0.6083</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-3.396</v>
+        <v>-3.1175</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.3638</v>
+        <v>-2.9544</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0322</v>
+        <v>-0.1631</v>
       </c>
       <c r="G17" t="n">
         <v>-0.8357</v>
@@ -1780,13 +1780,13 @@
         <v>2.3502</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1686</v>
+        <v>-0.8901</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0692</v>
+        <v>-0.6599</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0994</v>
+        <v>-0.2302</v>
       </c>
       <c r="V17" t="n">
         <v>-0.6083</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-4.574</v>
+        <v>-3.1645</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.4993</v>
+        <v>-0.6806</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.0747</v>
+        <v>-2.4839</v>
       </c>
       <c r="G18" t="n">
         <v>-3.3232</v>
@@ -1858,13 +1858,13 @@
         <v>1.9585</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.9559</v>
+        <v>-1.5464</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.6633</v>
+        <v>-0.8446</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.2927</v>
+        <v>-0.7018</v>
       </c>
       <c r="V18" t="n">
         <v>-0.0576</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-5.6487</v>
+        <v>-4.9407</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.8108</v>
+        <v>-3.5038</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.8379</v>
+        <v>-1.4369</v>
       </c>
       <c r="G19" t="n">
         <v>-5.736</v>
@@ -1936,13 +1936,13 @@
         <v>2.1543</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.8551</v>
+        <v>-2.1471</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.6633</v>
+        <v>-1.3562</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.1919</v>
+        <v>-0.7909</v>
       </c>
       <c r="V19" t="n">
         <v>1.7673</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-10.7436</v>
+        <v>-10.0613</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.908399999999999</v>
+        <v>-2.908300000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>-7.835300000000001</v>
+        <v>-7.153</v>
       </c>
       <c r="G20" t="n">
         <v>-3.250400000000001</v>
@@ -2014,13 +2014,13 @@
         <v>15.6679</v>
       </c>
       <c r="S20" t="n">
-        <v>-8.0427</v>
+        <v>-7.3605</v>
       </c>
       <c r="T20" t="n">
-        <v>-4.9375</v>
+        <v>-4.9374</v>
       </c>
       <c r="U20" t="n">
-        <v>-3.1055</v>
+        <v>-2.4229</v>
       </c>
       <c r="V20" t="n">
         <v>-2.3882</v>
